--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793156</v>
       </c>
       <c r="B2" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793152</v>
       </c>
       <c r="B3" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>128793231</v>
       </c>
       <c r="B6" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>128793155</v>
       </c>
       <c r="B7" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793156</v>
       </c>
       <c r="B2" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793152</v>
       </c>
       <c r="B3" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128793228</v>
       </c>
       <c r="B4" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128793229</v>
       </c>
       <c r="B5" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>128793231</v>
       </c>
       <c r="B6" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>128793155</v>
       </c>
       <c r="B7" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793156</v>
       </c>
       <c r="B2" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793152</v>
       </c>
       <c r="B3" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128793228</v>
       </c>
       <c r="B4" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>128793231</v>
       </c>
       <c r="B6" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>128793155</v>
       </c>
       <c r="B7" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793156</v>
       </c>
       <c r="B2" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793152</v>
       </c>
       <c r="B3" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>128793231</v>
       </c>
       <c r="B6" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>128793155</v>
       </c>
       <c r="B7" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1263,6 +1263,216 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128918664</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92794</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tallträsket, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>746584</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7161996</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128918639</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92788</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tallträsket, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>746568</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7161933</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793156</v>
       </c>
       <c r="B2" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793152</v>
       </c>
       <c r="B3" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128793228</v>
       </c>
       <c r="B4" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128793229</v>
       </c>
       <c r="B5" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>128793231</v>
       </c>
       <c r="B6" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>128793155</v>
       </c>
       <c r="B7" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128918664</v>
       </c>
       <c r="B8" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>128918639</v>
       </c>
       <c r="B9" t="n">
-        <v>92788</v>
+        <v>92792</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793156</v>
       </c>
       <c r="B2" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793152</v>
       </c>
       <c r="B3" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128793228</v>
       </c>
       <c r="B4" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128793229</v>
       </c>
       <c r="B5" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>128793231</v>
       </c>
       <c r="B6" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>128793155</v>
       </c>
       <c r="B7" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128918664</v>
       </c>
       <c r="B8" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>128918639</v>
       </c>
       <c r="B9" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793156</v>
       </c>
       <c r="B2" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793152</v>
       </c>
       <c r="B3" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>128793231</v>
       </c>
       <c r="B6" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>128793155</v>
       </c>
       <c r="B7" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128918664</v>
       </c>
       <c r="B8" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>128918639</v>
       </c>
       <c r="B9" t="n">
-        <v>92805</v>
+        <v>92810</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793156</v>
       </c>
       <c r="B2" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793152</v>
       </c>
       <c r="B3" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128793228</v>
       </c>
       <c r="B4" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>128793231</v>
       </c>
       <c r="B6" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>128793155</v>
       </c>
       <c r="B7" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128918664</v>
       </c>
       <c r="B8" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>128918639</v>
       </c>
       <c r="B9" t="n">
-        <v>92810</v>
+        <v>92813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793156</v>
       </c>
       <c r="B2" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793152</v>
       </c>
       <c r="B3" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128793228</v>
       </c>
       <c r="B4" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128793229</v>
       </c>
       <c r="B5" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>128793231</v>
       </c>
       <c r="B6" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>128793155</v>
       </c>
       <c r="B7" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128918664</v>
       </c>
       <c r="B8" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>128918639</v>
       </c>
       <c r="B9" t="n">
-        <v>92813</v>
+        <v>92820</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793156</v>
       </c>
       <c r="B2" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793152</v>
       </c>
       <c r="B3" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>128793231</v>
       </c>
       <c r="B6" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>128793155</v>
       </c>
       <c r="B7" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128918664</v>
       </c>
       <c r="B8" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>128918639</v>
       </c>
       <c r="B9" t="n">
-        <v>92820</v>
+        <v>92827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793156</v>
       </c>
       <c r="B2" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793152</v>
       </c>
       <c r="B3" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128793228</v>
       </c>
       <c r="B4" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128793229</v>
       </c>
       <c r="B5" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>128793231</v>
       </c>
       <c r="B6" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>128793155</v>
       </c>
       <c r="B7" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128918664</v>
       </c>
       <c r="B8" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>128918639</v>
       </c>
       <c r="B9" t="n">
-        <v>92827</v>
+        <v>92829</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128793156</v>
       </c>
       <c r="B2" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128793152</v>
       </c>
       <c r="B3" t="n">
-        <v>92839</v>
+        <v>92825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>128793231</v>
       </c>
       <c r="B6" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>128793155</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>128918664</v>
       </c>
       <c r="B8" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>128918639</v>
       </c>
       <c r="B9" t="n">
-        <v>92829</v>
+        <v>92815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>128918664</v>
       </c>
       <c r="B8" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>128918639</v>
       </c>
       <c r="B9" t="n">
-        <v>92815</v>
+        <v>92816</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>128918664</v>
       </c>
       <c r="B8" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>128918639</v>
       </c>
       <c r="B9" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>128918664</v>
       </c>
       <c r="B8" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>128918639</v>
       </c>
       <c r="B9" t="n">
-        <v>92819</v>
+        <v>92821</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -1268,7 +1268,7 @@
         <v>128918664</v>
       </c>
       <c r="B8" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>128918639</v>
       </c>
       <c r="B9" t="n">
-        <v>92821</v>
+        <v>92825</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -675,45 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128793156</v>
+        <v>128918639</v>
       </c>
       <c r="B2" t="n">
-        <v>92821</v>
+        <v>93191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tallträsk, Vb</t>
+          <t>Tallträsket, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746534</v>
+        <v>746568</v>
       </c>
       <c r="R2" t="n">
-        <v>7161946</v>
+        <v>7161933</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,50 +761,51 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128793152</v>
+        <v>128793155</v>
       </c>
       <c r="B3" t="n">
-        <v>92825</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746581</v>
+        <v>746565</v>
       </c>
       <c r="R3" t="n">
-        <v>7161892</v>
+        <v>7162220</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128793228</v>
+        <v>128793156</v>
       </c>
       <c r="B4" t="n">
-        <v>79660</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Näset, Vb</t>
+          <t>Tallträsk, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746702</v>
+        <v>746534</v>
       </c>
       <c r="R4" t="n">
-        <v>7162137</v>
+        <v>7161946</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,65 +962,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128793229</v>
+        <v>128793231</v>
       </c>
       <c r="B5" t="n">
-        <v>56917</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Näset, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>746633</v>
+        <v>746564</v>
       </c>
       <c r="R5" t="n">
-        <v>7162187</v>
+        <v>7161882</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,14 +1071,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128793231</v>
+        <v>128918664</v>
       </c>
       <c r="B6" t="n">
-        <v>92821</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1100,16 +1100,23 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Näset, Vb</t>
+          <t>Tallträsket, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746564</v>
+        <v>746584</v>
       </c>
       <c r="R6" t="n">
-        <v>7161882</v>
+        <v>7161996</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,50 +1157,51 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128793155</v>
+        <v>128793152</v>
       </c>
       <c r="B7" t="n">
-        <v>92821</v>
+        <v>93201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1203,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746565</v>
+        <v>746581</v>
       </c>
       <c r="R7" t="n">
-        <v>7162220</v>
+        <v>7161892</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,52 +1273,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128918664</v>
+        <v>128793228</v>
       </c>
       <c r="B8" t="n">
-        <v>92831</v>
+        <v>79946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tallträsket, Vb</t>
+          <t>Näset, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>746584</v>
+        <v>746702</v>
       </c>
       <c r="R8" t="n">
-        <v>7161996</v>
+        <v>7162137</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1351,71 +1352,71 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128918639</v>
+        <v>128793229</v>
       </c>
       <c r="B9" t="n">
-        <v>92825</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tallträsket, Vb</t>
+          <t>Näset, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>746568</v>
+        <v>746633</v>
       </c>
       <c r="R9" t="n">
-        <v>7161933</v>
+        <v>7162187</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,19 +1457,18 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 45210-2025 artfynd.xlsx
+++ b/artfynd/A 45210-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918639</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128793155</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128793156</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128793231</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128918664</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128793152</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128793228</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,8 +1512,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128793229</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>